--- a/static/data/exports/Retro_UK_GE_2024.xlsx
+++ b/static/data/exports/Retro_UK_GE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="Q38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>53</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="Q52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>53</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="Q66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>53</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Q80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>53</v>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="Q94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>53</v>
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="Q120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>53</v>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="Q134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>53</v>
@@ -14093,7 +14093,7 @@
         </is>
       </c>
       <c r="Q220" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
         <v>53</v>
@@ -15411,11 +15411,11 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1492228</v>
+        <v>1492227</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Sardar Khan Pappu</t>
+          <t>Vepin Kumar Aggarwal</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Sardar Khan Pappu</t>
+          <t>Vepin Kumar Aggarwal</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -15473,11 +15473,11 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1492227</v>
+        <v>1492228</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Vepin Kumar Aggarwal</t>
+          <t>Sardar Khan Pappu</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Vepin Kumar Aggarwal</t>
+          <t>Sardar Khan Pappu</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -16961,11 +16961,11 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>1492253</v>
+        <v>1492252</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Sudesh Tomar</t>
+          <t>Sardar Khan Pappu</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Sudesh Tomar</t>
+          <t>Sardar Khan Pappu</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -17023,11 +17023,11 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>1492252</v>
+        <v>1492253</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Sardar Khan Pappu</t>
+          <t>Sudesh Tomar</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -17060,7 +17060,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Sardar Khan Pappu</t>
+          <t>Sudesh Tomar</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -17999,7 +17999,7 @@
         </is>
       </c>
       <c r="Q283" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R283" t="n">
         <v>53</v>
@@ -18929,7 +18929,7 @@
         </is>
       </c>
       <c r="Q298" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R298" t="n">
         <v>53</v>
@@ -19859,7 +19859,7 @@
         </is>
       </c>
       <c r="Q313" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R313" t="n">
         <v>53</v>
@@ -20371,11 +20371,11 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>1492308</v>
+        <v>1492307</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Karan Singh Saini Engineer</t>
+          <t>Akram Hussain</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Karan Singh Saini Engineer</t>
+          <t>Akram Hussain</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -20433,11 +20433,11 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>1492307</v>
+        <v>1492308</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Akram Hussain</t>
+          <t>Karan Singh Saini Engineer</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>Akram Hussain</t>
+          <t>Karan Singh Saini Engineer</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -20789,7 +20789,7 @@
         </is>
       </c>
       <c r="Q328" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R328" t="n">
         <v>53</v>
@@ -21549,11 +21549,11 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>1492326</v>
+        <v>1492327</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Avnish Kumar</t>
+          <t>Ashish Dhyani</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21586,7 +21586,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Avnish Kumar</t>
+          <t>Ashish Dhyani</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -21611,11 +21611,11 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1492327</v>
+        <v>1492326</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Ashish Dhyani</t>
+          <t>Avnish Kumar</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21648,7 +21648,7 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Ashish Dhyani</t>
+          <t>Avnish Kumar</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -21781,7 +21781,7 @@
         </is>
       </c>
       <c r="Q344" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R344" t="n">
         <v>53</v>
@@ -22711,7 +22711,7 @@
         </is>
       </c>
       <c r="Q359" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R359" t="n">
         <v>53</v>
@@ -23641,7 +23641,7 @@
         </is>
       </c>
       <c r="Q374" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R374" t="n">
         <v>53</v>
@@ -24571,7 +24571,7 @@
         </is>
       </c>
       <c r="Q389" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R389" t="n">
         <v>53</v>
@@ -25439,7 +25439,7 @@
         </is>
       </c>
       <c r="Q403" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R403" t="n">
         <v>53</v>
@@ -26369,7 +26369,7 @@
         </is>
       </c>
       <c r="Q418" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R418" t="n">
         <v>53</v>
@@ -27361,7 +27361,7 @@
         </is>
       </c>
       <c r="Q434" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R434" t="n">
         <v>53</v>
@@ -28291,7 +28291,7 @@
         </is>
       </c>
       <c r="Q449" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R449" t="n">
         <v>53</v>
@@ -29159,7 +29159,7 @@
         </is>
       </c>
       <c r="Q463" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R463" t="n">
         <v>53</v>
@@ -30089,7 +30089,7 @@
         </is>
       </c>
       <c r="Q478" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R478" t="n">
         <v>53</v>
@@ -30957,7 +30957,7 @@
         </is>
       </c>
       <c r="Q492" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R492" t="n">
         <v>53</v>
@@ -31825,7 +31825,7 @@
         </is>
       </c>
       <c r="Q506" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R506" t="n">
         <v>53</v>
@@ -32693,7 +32693,7 @@
         </is>
       </c>
       <c r="Q520" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R520" t="n">
         <v>53</v>
@@ -33561,7 +33561,7 @@
         </is>
       </c>
       <c r="Q534" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R534" t="n">
         <v>53</v>
@@ -33949,20 +33949,20 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>1492526</v>
+        <v>1492527</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Arjun Singh</t>
+          <t>Deependra Singh Negi</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>AKBRPRVP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>16163</v>
+        <v>16059</v>
       </c>
       <c r="E541" t="n">
         <v>83</v>
@@ -33986,12 +33986,12 @@
       </c>
       <c r="K541" t="inlineStr">
         <is>
-          <t>Arjun Singh</t>
+          <t>Deependra Singh Negi</t>
         </is>
       </c>
       <c r="L541" t="inlineStr">
         <is>
-          <t>AKBRPRVP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q541" t="b">
@@ -34011,20 +34011,20 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>1492527</v>
+        <v>1492526</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Deependra Singh Negi</t>
+          <t>Arjun Singh</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AKBRPRVP</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>16059</v>
+        <v>16163</v>
       </c>
       <c r="E542" t="n">
         <v>83</v>
@@ -34048,12 +34048,12 @@
       </c>
       <c r="K542" t="inlineStr">
         <is>
-          <t>Deependra Singh Negi</t>
+          <t>Arjun Singh</t>
         </is>
       </c>
       <c r="L542" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>AKBRPRVP</t>
         </is>
       </c>
       <c r="Q542" t="b">
@@ -34429,7 +34429,7 @@
         </is>
       </c>
       <c r="Q548" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R548" t="n">
         <v>53</v>
@@ -34941,20 +34941,20 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>1492544</v>
+        <v>1492542</v>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Sureshi Devi</t>
+          <t>Dr Mukesh Pant</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>SaSP</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>16162</v>
+        <v>16097</v>
       </c>
       <c r="E557" t="n">
         <v>65</v>
@@ -34978,12 +34978,12 @@
       </c>
       <c r="K557" t="inlineStr">
         <is>
-          <t>Sureshi Devi</t>
+          <t>Dr Mukesh Pant</t>
         </is>
       </c>
       <c r="L557" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>SaSP</t>
         </is>
       </c>
       <c r="Q557" t="b">
@@ -35065,20 +35065,20 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>1492542</v>
+        <v>1492544</v>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Dr Mukesh Pant</t>
+          <t>Sureshi Devi</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>SaSP</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>16097</v>
+        <v>16162</v>
       </c>
       <c r="E559" t="n">
         <v>65</v>
@@ -35102,12 +35102,12 @@
       </c>
       <c r="K559" t="inlineStr">
         <is>
-          <t>Dr Mukesh Pant</t>
+          <t>Sureshi Devi</t>
         </is>
       </c>
       <c r="L559" t="inlineStr">
         <is>
-          <t>SaSP</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="Q559" t="b">
@@ -39033,20 +39033,20 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>1492608</v>
+        <v>1492609</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Kiran Arya</t>
+          <t>Dr Pramod Kumar</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>UPP</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="D623" t="n">
-        <v>16166</v>
+        <v>16162</v>
       </c>
       <c r="E623" t="n">
         <v>258</v>
@@ -39070,12 +39070,12 @@
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>Kiran Arya</t>
+          <t>Dr Pramod Kumar</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>UPP</t>
+          <t>PPID</t>
         </is>
       </c>
       <c r="Q623" t="b">
@@ -39095,20 +39095,20 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>1492609</v>
+        <v>1492608</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Dr Pramod Kumar</t>
+          <t>Kiran Arya</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>UPP</t>
         </is>
       </c>
       <c r="D624" t="n">
-        <v>16162</v>
+        <v>16166</v>
       </c>
       <c r="E624" t="n">
         <v>258</v>
@@ -39132,12 +39132,12 @@
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>Dr Pramod Kumar</t>
+          <t>Kiran Arya</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>PPID</t>
+          <t>UPP</t>
         </is>
       </c>
       <c r="Q624" t="b">
@@ -45651,7 +45651,7 @@
         </is>
       </c>
       <c r="Q729" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R729" t="n">
         <v>53</v>
